--- a/grupos/3APM - Estadisticos 20211.xlsx
+++ b/grupos/3APM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="117">
   <si>
     <t>Materia</t>
   </si>
@@ -161,6 +161,9 @@
     <t>Castro Vasquez Julieta</t>
   </si>
   <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
@@ -170,9 +173,6 @@
     <t>De Jesús Orduña Sofía del Pilar</t>
   </si>
   <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
     <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
@@ -188,6 +188,15 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CUEVAS</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
     <t>BACILIO</t>
   </si>
   <si>
@@ -200,33 +209,45 @@
     <t>CORTES</t>
   </si>
   <si>
-    <t>CUEVAS</t>
-  </si>
-  <si>
     <t>CRUZ</t>
   </si>
   <si>
     <t>GERARDO</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>HERRERA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>MIRANDA</t>
+  </si>
+  <si>
     <t>NAMIGTLE</t>
   </si>
   <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>TORRES</t>
+  </si>
+  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
+    <t>URBANO</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
     <t>VERA</t>
   </si>
   <si>
@@ -248,9 +269,6 @@
     <t>CONTRERAS</t>
   </si>
   <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
     <t>PIMENTEL</t>
   </si>
   <si>
@@ -260,6 +278,9 @@
     <t>CASTRO</t>
   </si>
   <si>
+    <t>AGUIRRE</t>
+  </si>
+  <si>
     <t>IXTLA</t>
   </si>
   <si>
@@ -269,12 +290,21 @@
     <t>DE JESUS</t>
   </si>
   <si>
+    <t>ESTRELLA</t>
+  </si>
+  <si>
     <t>MOLOHUA</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>PONCE</t>
   </si>
   <si>
@@ -293,9 +323,6 @@
     <t>ALFREDO</t>
   </si>
   <si>
-    <t>CESAR</t>
-  </si>
-  <si>
     <t>ISYSS MONSERRATH</t>
   </si>
   <si>
@@ -305,6 +332,9 @@
     <t>EDUARDO</t>
   </si>
   <si>
+    <t>MARIAM GUADALUPE</t>
+  </si>
+  <si>
     <t>JESUS</t>
   </si>
   <si>
@@ -320,9 +350,15 @@
     <t>ANGEL ALDAHIR</t>
   </si>
   <si>
+    <t>ESTEFANI</t>
+  </si>
+  <si>
     <t>EMILIO</t>
   </si>
   <si>
+    <t>INGRID</t>
+  </si>
+  <si>
     <t>JAHEL</t>
   </si>
   <si>
@@ -333,42 +369,6 @@
   </si>
   <si>
     <t>ANGELA MONTSERRAT</t>
-  </si>
-  <si>
-    <t>MIRANDA</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>URBANO</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>AGUIRRE</t>
-  </si>
-  <si>
-    <t>ESTRELLA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MARIAM GUADALUPE</t>
-  </si>
-  <si>
-    <t>ESTEFANI</t>
-  </si>
-  <si>
-    <t>INGRID</t>
   </si>
 </sst>
 </file>
@@ -866,28 +866,28 @@
         <v>8</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -908,22 +908,22 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>8</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -931,7 +931,7 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C5">
         <v>6</v>
@@ -946,25 +946,25 @@
         <v>6</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H5">
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -985,13 +985,13 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W5">
         <v>6</v>
@@ -1000,7 +1000,7 @@
         <v>6</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1020,28 +1020,28 @@
         <v>7</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G6">
         <v>9</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1062,22 +1062,22 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>7</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1085,7 +1085,7 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C7">
         <v>7</v>
@@ -1097,10 +1097,10 @@
         <v>6</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H7">
         <v>-1</v>
@@ -1109,16 +1109,16 @@
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1139,7 +1139,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U7">
         <v>7</v>
@@ -1151,10 +1151,10 @@
         <v>6</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1162,10 +1162,10 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -1174,10 +1174,10 @@
         <v>5</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H8">
         <v>-1</v>
@@ -1186,16 +1186,16 @@
         <v>-1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K8">
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1216,10 +1216,10 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V8">
         <v>5</v>
@@ -1228,10 +1228,10 @@
         <v>5</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1239,7 +1239,7 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C9">
         <v>6</v>
@@ -1251,28 +1251,28 @@
         <v>5</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H9">
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1293,22 +1293,22 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U9">
         <v>6</v>
       </c>
       <c r="V9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>5</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1316,10 +1316,10 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D10">
         <v>5</v>
@@ -1328,28 +1328,28 @@
         <v>-1</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1370,22 +1370,22 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>-1</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1393,10 +1393,10 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D11">
         <v>5</v>
@@ -1405,10 +1405,10 @@
         <v>5</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H11">
         <v>-1</v>
@@ -1417,16 +1417,16 @@
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K11">
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1447,10 +1447,10 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V11">
         <v>5</v>
@@ -1459,10 +1459,10 @@
         <v>5</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1488,22 +1488,22 @@
         <v>10</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1524,13 +1524,13 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W12">
         <v>9</v>
@@ -1559,28 +1559,28 @@
         <v>8</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1607,16 +1607,16 @@
         <v>6</v>
       </c>
       <c r="V13">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>8</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1639,25 +1639,25 @@
         <v>7</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1684,7 +1684,7 @@
         <v>6</v>
       </c>
       <c r="V14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W14">
         <v>7</v>
@@ -1693,7 +1693,7 @@
         <v>7</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1701,7 +1701,7 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -1713,7 +1713,7 @@
         <v>9</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G15">
         <v>7</v>
@@ -1722,19 +1722,19 @@
         <v>-1</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1755,19 +1755,19 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U15">
         <v>6</v>
       </c>
       <c r="V15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W15">
         <v>9</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>7</v>
@@ -1778,10 +1778,10 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D16">
         <v>5</v>
@@ -1790,7 +1790,7 @@
         <v>5</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H16">
         <v>-1</v>
@@ -1799,13 +1799,13 @@
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1823,10 +1823,10 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V16">
         <v>5</v>
@@ -1835,7 +1835,7 @@
         <v>5</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1843,7 +1843,7 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C17">
         <v>8</v>
@@ -1858,25 +1858,25 @@
         <v>6</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1897,10 +1897,10 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V17">
         <v>7</v>
@@ -1909,10 +1909,10 @@
         <v>7</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1938,22 +1938,22 @@
         <v>9</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1980,13 +1980,13 @@
         <v>9</v>
       </c>
       <c r="V18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W18">
         <v>10</v>
       </c>
       <c r="X18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y18">
         <v>9</v>
@@ -2000,7 +2000,7 @@
         <v>8</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D19">
         <v>5</v>
@@ -2012,25 +2012,25 @@
         <v>7</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I19">
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2054,7 +2054,7 @@
         <v>8</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V19">
         <v>5</v>
@@ -2063,10 +2063,10 @@
         <v>5</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2092,22 +2092,22 @@
         <v>10</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2131,19 +2131,19 @@
         <v>9</v>
       </c>
       <c r="U20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W20">
         <v>6</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2166,25 +2166,25 @@
         <v>6</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2208,7 +2208,7 @@
         <v>9</v>
       </c>
       <c r="U21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>9</v>
@@ -2217,10 +2217,10 @@
         <v>8</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2246,22 +2246,22 @@
         <v>7</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2285,16 +2285,16 @@
         <v>9</v>
       </c>
       <c r="U22">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>9</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y22">
         <v>7</v>
@@ -2305,7 +2305,7 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C23">
         <v>6</v>
@@ -2317,28 +2317,28 @@
         <v>6</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2359,22 +2359,22 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U23">
         <v>6</v>
       </c>
       <c r="V23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W23">
         <v>6</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2400,22 +2400,22 @@
         <v>9</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K24">
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2439,7 +2439,7 @@
         <v>10</v>
       </c>
       <c r="U24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V24">
         <v>10</v>
@@ -2451,7 +2451,7 @@
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2477,22 +2477,22 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K25">
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2516,10 +2516,10 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>10</v>
@@ -2548,28 +2548,28 @@
         <v>5</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2596,16 +2596,16 @@
         <v>6</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>5</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2628,25 +2628,25 @@
         <v>9</v>
       </c>
       <c r="G27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K27">
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2667,13 +2667,13 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U27">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W27">
         <v>6</v>
@@ -2682,7 +2682,7 @@
         <v>9</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2690,7 +2690,7 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C28">
         <v>6</v>
@@ -2702,28 +2702,28 @@
         <v>6</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H28">
         <v>-1</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2744,22 +2744,22 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U28">
         <v>6</v>
       </c>
       <c r="V28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W28">
         <v>6</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2824,30 +2824,30 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>33.33</v>
+        <v>45.83</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>54.17</v>
       </c>
       <c r="H2">
-        <v>8.9</v>
+        <v>6.8</v>
       </c>
       <c r="I2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>66.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>47</v>
@@ -2856,30 +2856,30 @@
         <v>25</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>52</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>48</v>
@@ -2888,19 +2888,19 @@
         <v>25</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="G4">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2911,7 +2911,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>49</v>
@@ -2920,30 +2920,30 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="I5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>50</v>
@@ -2955,22 +2955,22 @@
         <v>18</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6">
         <v>72</v>
       </c>
       <c r="G6">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -2984,25 +2984,25 @@
         <v>25</v>
       </c>
       <c r="D7">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3012,7 +3012,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3041,922 +3041,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920336</v>
+        <v>20330051920340</v>
       </c>
       <c r="B2" t="s">
         <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920336</v>
-      </c>
-      <c r="B3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920337</v>
-      </c>
-      <c r="B4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920337</v>
-      </c>
-      <c r="B5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920263</v>
-      </c>
-      <c r="B6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920339</v>
-      </c>
-      <c r="B7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920339</v>
-      </c>
-      <c r="B8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920339</v>
-      </c>
-      <c r="B9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" t="s">
-        <v>75</v>
-      </c>
-      <c r="D9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920340</v>
-      </c>
-      <c r="B10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" t="s">
-        <v>76</v>
-      </c>
-      <c r="D10" t="s">
-        <v>91</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920340</v>
-      </c>
-      <c r="B11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" t="s">
-        <v>76</v>
-      </c>
-      <c r="D11" t="s">
-        <v>91</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920340</v>
-      </c>
-      <c r="B12" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" t="s">
-        <v>76</v>
-      </c>
-      <c r="D12" t="s">
-        <v>91</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920340</v>
-      </c>
-      <c r="B13" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" t="s">
-        <v>76</v>
-      </c>
-      <c r="D13" t="s">
-        <v>91</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920340</v>
-      </c>
-      <c r="B14" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" t="s">
-        <v>76</v>
-      </c>
-      <c r="D14" t="s">
-        <v>91</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920341</v>
-      </c>
-      <c r="B15" t="s">
-        <v>61</v>
-      </c>
-      <c r="C15" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15" t="s">
-        <v>92</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920341</v>
-      </c>
-      <c r="B16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" t="s">
-        <v>77</v>
-      </c>
-      <c r="D16" t="s">
-        <v>92</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920341</v>
-      </c>
-      <c r="B17" t="s">
-        <v>61</v>
-      </c>
-      <c r="C17" t="s">
-        <v>77</v>
-      </c>
-      <c r="D17" t="s">
-        <v>92</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920342</v>
-      </c>
-      <c r="B18" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" t="s">
-        <v>78</v>
-      </c>
-      <c r="D18" t="s">
-        <v>93</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920342</v>
-      </c>
-      <c r="B19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C19" t="s">
-        <v>78</v>
-      </c>
-      <c r="D19" t="s">
-        <v>93</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920342</v>
-      </c>
-      <c r="B20" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" t="s">
-        <v>93</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920342</v>
-      </c>
-      <c r="B21" t="s">
-        <v>61</v>
-      </c>
-      <c r="C21" t="s">
-        <v>78</v>
-      </c>
-      <c r="D21" t="s">
-        <v>93</v>
-      </c>
-      <c r="E21" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920343</v>
-      </c>
-      <c r="B22" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22" t="s">
-        <v>79</v>
-      </c>
-      <c r="D22" t="s">
-        <v>94</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920343</v>
-      </c>
-      <c r="B23" t="s">
-        <v>62</v>
-      </c>
-      <c r="C23" t="s">
-        <v>79</v>
-      </c>
-      <c r="D23" t="s">
-        <v>94</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>20330051920343</v>
-      </c>
-      <c r="B24" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" t="s">
-        <v>79</v>
-      </c>
-      <c r="D24" t="s">
-        <v>94</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>20330051920343</v>
-      </c>
-      <c r="B25" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" t="s">
-        <v>79</v>
-      </c>
-      <c r="D25" t="s">
-        <v>94</v>
-      </c>
-      <c r="E25" t="s">
-        <v>5</v>
-      </c>
-      <c r="F25" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>19330051420540</v>
-      </c>
-      <c r="B26" t="s">
-        <v>63</v>
-      </c>
-      <c r="C26" t="s">
-        <v>61</v>
-      </c>
-      <c r="D26" t="s">
-        <v>95</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>19330051420540</v>
-      </c>
-      <c r="B27" t="s">
-        <v>63</v>
-      </c>
-      <c r="C27" t="s">
-        <v>61</v>
-      </c>
-      <c r="D27" t="s">
-        <v>95</v>
-      </c>
-      <c r="E27" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>19330051420540</v>
-      </c>
-      <c r="B28" t="s">
-        <v>63</v>
-      </c>
-      <c r="C28" t="s">
-        <v>61</v>
-      </c>
-      <c r="D28" t="s">
-        <v>95</v>
-      </c>
-      <c r="E28" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>20330051920345</v>
-      </c>
-      <c r="B29" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" t="s">
-        <v>80</v>
-      </c>
-      <c r="D29" t="s">
-        <v>96</v>
-      </c>
-      <c r="E29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>20330051920345</v>
-      </c>
-      <c r="B30" t="s">
-        <v>64</v>
-      </c>
-      <c r="C30" t="s">
-        <v>80</v>
-      </c>
-      <c r="D30" t="s">
-        <v>96</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>20330051920381</v>
-      </c>
-      <c r="B31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" t="s">
-        <v>67</v>
-      </c>
-      <c r="D31" t="s">
-        <v>97</v>
-      </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>20330051920346</v>
-      </c>
-      <c r="B32" t="s">
-        <v>64</v>
-      </c>
-      <c r="C32" t="s">
-        <v>81</v>
-      </c>
-      <c r="D32" t="s">
-        <v>95</v>
-      </c>
-      <c r="E32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>20330051920346</v>
-      </c>
-      <c r="B33" t="s">
-        <v>64</v>
-      </c>
-      <c r="C33" t="s">
-        <v>81</v>
-      </c>
-      <c r="D33" t="s">
-        <v>95</v>
-      </c>
-      <c r="E33" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>20330051920347</v>
-      </c>
-      <c r="B34" t="s">
-        <v>65</v>
-      </c>
-      <c r="C34" t="s">
-        <v>82</v>
-      </c>
-      <c r="D34" t="s">
-        <v>98</v>
-      </c>
-      <c r="E34" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>20330051920347</v>
-      </c>
-      <c r="B35" t="s">
-        <v>65</v>
-      </c>
-      <c r="C35" t="s">
-        <v>82</v>
-      </c>
-      <c r="D35" t="s">
-        <v>98</v>
-      </c>
-      <c r="E35" t="s">
-        <v>5</v>
-      </c>
-      <c r="F35" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>20330051920349</v>
-      </c>
-      <c r="B36" t="s">
-        <v>66</v>
-      </c>
-      <c r="C36" t="s">
-        <v>83</v>
-      </c>
-      <c r="D36" t="s">
-        <v>99</v>
-      </c>
-      <c r="E36" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>20330051920349</v>
-      </c>
-      <c r="B37" t="s">
-        <v>66</v>
-      </c>
-      <c r="C37" t="s">
-        <v>83</v>
-      </c>
-      <c r="D37" t="s">
-        <v>99</v>
-      </c>
-      <c r="E37" t="s">
-        <v>6</v>
-      </c>
-      <c r="F37" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>20330051920352</v>
-      </c>
-      <c r="B38" t="s">
-        <v>67</v>
-      </c>
-      <c r="C38" t="s">
-        <v>84</v>
-      </c>
-      <c r="D38" t="s">
-        <v>100</v>
-      </c>
-      <c r="E38" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>20330051920354</v>
-      </c>
-      <c r="B39" t="s">
-        <v>68</v>
-      </c>
-      <c r="C39" t="s">
-        <v>63</v>
-      </c>
-      <c r="D39" t="s">
-        <v>101</v>
-      </c>
-      <c r="E39" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>20330051920354</v>
-      </c>
-      <c r="B40" t="s">
-        <v>68</v>
-      </c>
-      <c r="C40" t="s">
-        <v>63</v>
-      </c>
-      <c r="D40" t="s">
-        <v>101</v>
-      </c>
-      <c r="E40" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>20330051920354</v>
-      </c>
-      <c r="B41" t="s">
-        <v>68</v>
-      </c>
-      <c r="C41" t="s">
-        <v>63</v>
-      </c>
-      <c r="D41" t="s">
-        <v>101</v>
-      </c>
-      <c r="E41" t="s">
-        <v>5</v>
-      </c>
-      <c r="F41" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>20330051920356</v>
-      </c>
-      <c r="B42" t="s">
-        <v>69</v>
-      </c>
-      <c r="C42" t="s">
-        <v>85</v>
-      </c>
-      <c r="D42" t="s">
-        <v>102</v>
-      </c>
-      <c r="E42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>20330051920356</v>
-      </c>
-      <c r="B43" t="s">
-        <v>69</v>
-      </c>
-      <c r="C43" t="s">
-        <v>85</v>
-      </c>
-      <c r="D43" t="s">
-        <v>102</v>
-      </c>
-      <c r="E43" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>20330051920357</v>
-      </c>
-      <c r="B44" t="s">
-        <v>70</v>
-      </c>
-      <c r="C44" t="s">
-        <v>86</v>
-      </c>
-      <c r="D44" t="s">
-        <v>103</v>
-      </c>
-      <c r="E44" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>20330051920383</v>
-      </c>
-      <c r="B45" t="s">
-        <v>71</v>
-      </c>
-      <c r="C45" t="s">
-        <v>87</v>
-      </c>
-      <c r="D45" t="s">
-        <v>104</v>
-      </c>
-      <c r="E45" t="s">
-        <v>9</v>
-      </c>
-      <c r="F45" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>20330051920383</v>
-      </c>
-      <c r="B46" t="s">
-        <v>71</v>
-      </c>
-      <c r="C46" t="s">
-        <v>87</v>
-      </c>
-      <c r="D46" t="s">
-        <v>104</v>
-      </c>
-      <c r="E46" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>20330051920383</v>
-      </c>
-      <c r="B47" t="s">
-        <v>71</v>
-      </c>
-      <c r="C47" t="s">
-        <v>87</v>
-      </c>
-      <c r="D47" t="s">
-        <v>104</v>
-      </c>
-      <c r="E47" t="s">
-        <v>5</v>
-      </c>
-      <c r="F47" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -3995,169 +3095,169 @@
         <v>20330051920340</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920342</v>
+        <v>20330051920336</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920343</v>
+        <v>20330051920337</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920339</v>
+        <v>20330051920263</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920341</v>
+        <v>20330051920339</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051420540</v>
+        <v>20330051920341</v>
       </c>
       <c r="B7" t="s">
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920354</v>
+        <v>20330051920342</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920383</v>
+        <v>20330051920343</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920336</v>
+        <v>20330051920344</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920337</v>
+        <v>19330051420540</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -4165,118 +3265,118 @@
         <v>20330051920345</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920346</v>
+        <v>20330051920381</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920347</v>
+        <v>20330051920346</v>
       </c>
       <c r="B14" t="s">
         <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920349</v>
+        <v>20330051920347</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920356</v>
+        <v>20330051920348</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920263</v>
+        <v>20330051920349</v>
       </c>
       <c r="B17" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C17" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="D17" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920381</v>
+        <v>20330051920350</v>
       </c>
       <c r="B18" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D18" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -4284,47 +3384,47 @@
         <v>20330051920352</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D19" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920357</v>
+        <v>20330051920353</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D20" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920344</v>
+        <v>20330051920354</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="D21" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -4332,16 +3432,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920348</v>
+        <v>20330051920355</v>
       </c>
       <c r="B22" t="s">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="D22" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -4349,16 +3449,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920350</v>
+        <v>20330051920382</v>
       </c>
       <c r="B23" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D23" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -4366,16 +3466,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920353</v>
+        <v>20330051920356</v>
       </c>
       <c r="B24" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="C24" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="D24" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -4383,16 +3483,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920355</v>
+        <v>20330051920357</v>
       </c>
       <c r="B25" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="C25" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="D25" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -4400,16 +3500,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920382</v>
+        <v>20330051920383</v>
       </c>
       <c r="B26" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="C26" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="D26" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -4422,7 +3522,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4454,39 +3554,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920336</v>
+        <v>20330051920337</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920336</v>
+        <v>20330051920337</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -4495,27 +3595,27 @@
         <v>46</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920263</v>
+        <v>20330051920336</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4523,48 +3623,48 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920263</v>
+        <v>20330051920345</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920347</v>
+        <v>20330051920346</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -4572,13 +3672,13 @@
         <v>20330051920347</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -4587,76 +3687,7 @@
         <v>46</v>
       </c>
       <c r="G7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920381</v>
-      </c>
-      <c r="B8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D8" t="s">
-        <v>97</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920352</v>
-      </c>
-      <c r="B9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" t="s">
-        <v>84</v>
-      </c>
-      <c r="D9" t="s">
-        <v>100</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920357</v>
-      </c>
-      <c r="B10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" t="s">
-        <v>86</v>
-      </c>
-      <c r="D10" t="s">
-        <v>103</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/3APM - Estadisticos 20211.xlsx
+++ b/grupos/3APM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="117">
   <si>
     <t>Materia</t>
   </si>
@@ -188,139 +188,139 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>BACILIO</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
     <t>CUEVAS</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GERARDO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MIRANDA</t>
+  </si>
+  <si>
+    <t>NAMIGTLE</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>URBANO</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>XILCAHUA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ATILANO</t>
+  </si>
+  <si>
+    <t>VILLALBA</t>
+  </si>
+  <si>
+    <t>ZAVALETA</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
     <t>CUATRA</t>
   </si>
   <si>
+    <t>PIMENTEL</t>
+  </si>
+  <si>
+    <t>PALMA</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>AGUIRRE</t>
+  </si>
+  <si>
+    <t>IXTLA</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>ESTRELLA</t>
+  </si>
+  <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>PONCE</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>YAIR</t>
+  </si>
+  <si>
+    <t>ADAN</t>
+  </si>
+  <si>
+    <t>ALFREDO</t>
+  </si>
+  <si>
     <t>CESAR</t>
-  </si>
-  <si>
-    <t>BACILIO</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GERARDO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MIRANDA</t>
-  </si>
-  <si>
-    <t>NAMIGTLE</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>URBANO</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>XILCAHUA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ATILANO</t>
-  </si>
-  <si>
-    <t>VILLALBA</t>
-  </si>
-  <si>
-    <t>ZAVALETA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>PIMENTEL</t>
-  </si>
-  <si>
-    <t>PALMA</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>AGUIRRE</t>
-  </si>
-  <si>
-    <t>IXTLA</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>ESTRELLA</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>PONCE</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>YAIR</t>
-  </si>
-  <si>
-    <t>ADAN</t>
-  </si>
-  <si>
-    <t>ALFREDO</t>
   </si>
   <si>
     <t>ISYSS MONSERRATH</t>
@@ -881,7 +881,7 @@
         <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
         <v>7</v>
@@ -958,7 +958,7 @@
         <v>7</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
         <v>6</v>
@@ -994,7 +994,7 @@
         <v>6</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>6</v>
@@ -1035,7 +1035,7 @@
         <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
         <v>7</v>
@@ -1071,7 +1071,7 @@
         <v>7</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>7</v>
@@ -1112,7 +1112,7 @@
         <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -1148,7 +1148,7 @@
         <v>5</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X7">
         <v>5</v>
@@ -1189,7 +1189,7 @@
         <v>5</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L8">
         <v>5</v>
@@ -1266,7 +1266,7 @@
         <v>8</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L9">
         <v>6</v>
@@ -1325,7 +1325,7 @@
         <v>5</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -1343,7 +1343,7 @@
         <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
         <v>5</v>
@@ -1379,7 +1379,7 @@
         <v>8</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>5</v>
@@ -1420,7 +1420,7 @@
         <v>5</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L11">
         <v>5</v>
@@ -1497,7 +1497,7 @@
         <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
         <v>10</v>
@@ -1533,7 +1533,7 @@
         <v>10</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X12">
         <v>10</v>
@@ -1574,7 +1574,7 @@
         <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
         <v>5</v>
@@ -1610,7 +1610,7 @@
         <v>8</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X13">
         <v>7</v>
@@ -1651,7 +1651,7 @@
         <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
         <v>6</v>
@@ -1687,7 +1687,7 @@
         <v>8</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>7</v>
@@ -1728,7 +1728,7 @@
         <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
         <v>7</v>
@@ -1764,7 +1764,7 @@
         <v>6</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>7</v>
@@ -1802,7 +1802,7 @@
         <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
         <v>7</v>
@@ -1870,7 +1870,7 @@
         <v>7</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L17">
         <v>8</v>
@@ -1906,7 +1906,7 @@
         <v>7</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X17">
         <v>7</v>
@@ -1947,7 +1947,7 @@
         <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
         <v>7</v>
@@ -2024,7 +2024,7 @@
         <v>5</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L19">
         <v>5</v>
@@ -2101,7 +2101,7 @@
         <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L20">
         <v>9</v>
@@ -2137,7 +2137,7 @@
         <v>8</v>
       </c>
       <c r="W20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X20">
         <v>9</v>
@@ -2178,7 +2178,7 @@
         <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
         <v>8</v>
@@ -2255,7 +2255,7 @@
         <v>9</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
         <v>6</v>
@@ -2332,7 +2332,7 @@
         <v>5</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
         <v>5</v>
@@ -2368,7 +2368,7 @@
         <v>5</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X23">
         <v>5</v>
@@ -2409,7 +2409,7 @@
         <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
         <v>10</v>
@@ -2486,7 +2486,7 @@
         <v>7</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
         <v>10</v>
@@ -2563,7 +2563,7 @@
         <v>8</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L26">
         <v>5</v>
@@ -2640,7 +2640,7 @@
         <v>8</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L27">
         <v>8</v>
@@ -2676,7 +2676,7 @@
         <v>8</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>9</v>
@@ -2717,7 +2717,7 @@
         <v>5</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L28">
         <v>5</v>
@@ -2753,7 +2753,7 @@
         <v>5</v>
       </c>
       <c r="W28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X28">
         <v>5</v>
@@ -2856,25 +2856,25 @@
         <v>25</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="G3">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3012,7 +3012,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3037,26 +3037,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920340</v>
-      </c>
-      <c r="B2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -3092,30 +3072,30 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920340</v>
+        <v>20330051920336</v>
       </c>
       <c r="B2" t="s">
         <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920336</v>
+        <v>20330051920337</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
         <v>98</v>
@@ -3126,13 +3106,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920337</v>
+        <v>20330051920263</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
         <v>99</v>
@@ -3143,16 +3123,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920263</v>
+        <v>20330051920339</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -3160,16 +3140,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920339</v>
+        <v>20330051920340</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -3180,10 +3160,10 @@
         <v>20330051920341</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
         <v>101</v>
@@ -3197,10 +3177,10 @@
         <v>20330051920342</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
         <v>102</v>
@@ -3214,10 +3194,10 @@
         <v>20330051920343</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
         <v>103</v>
@@ -3231,10 +3211,10 @@
         <v>20330051920344</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
         <v>104</v>
@@ -3248,10 +3228,10 @@
         <v>19330051420540</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D11" t="s">
         <v>105</v>
@@ -3265,10 +3245,10 @@
         <v>20330051920345</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D12" t="s">
         <v>106</v>
@@ -3282,10 +3262,10 @@
         <v>20330051920381</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D13" t="s">
         <v>107</v>
@@ -3299,10 +3279,10 @@
         <v>20330051920346</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
         <v>105</v>
@@ -3316,10 +3296,10 @@
         <v>20330051920347</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s">
         <v>108</v>
@@ -3333,10 +3313,10 @@
         <v>20330051920348</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D16" t="s">
         <v>105</v>
@@ -3350,10 +3330,10 @@
         <v>20330051920349</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
         <v>109</v>
@@ -3367,10 +3347,10 @@
         <v>20330051920350</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D18" t="s">
         <v>110</v>
@@ -3384,10 +3364,10 @@
         <v>20330051920352</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D19" t="s">
         <v>111</v>
@@ -3401,10 +3381,10 @@
         <v>20330051920353</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D20" t="s">
         <v>112</v>
@@ -3418,10 +3398,10 @@
         <v>20330051920354</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C21" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D21" t="s">
         <v>113</v>
@@ -3435,10 +3415,10 @@
         <v>20330051920355</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C22" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D22" t="s">
         <v>108</v>
@@ -3452,10 +3432,10 @@
         <v>20330051920382</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C23" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D23" t="s">
         <v>102</v>
@@ -3469,10 +3449,10 @@
         <v>20330051920356</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D24" t="s">
         <v>114</v>
@@ -3486,10 +3466,10 @@
         <v>20330051920357</v>
       </c>
       <c r="B25" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D25" t="s">
         <v>115</v>
@@ -3503,10 +3483,10 @@
         <v>20330051920383</v>
       </c>
       <c r="B26" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C26" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D26" t="s">
         <v>116</v>
@@ -3522,7 +3502,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3557,13 +3537,13 @@
         <v>20330051920337</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -3580,13 +3560,13 @@
         <v>20330051920337</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -3600,22 +3580,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920336</v>
+        <v>20330051920340</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -3623,16 +3603,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920345</v>
+        <v>20330051920340</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -3646,22 +3626,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920346</v>
+        <v>20330051920336</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -3669,16 +3649,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920347</v>
+        <v>20330051920345</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -3687,6 +3667,52 @@
         <v>46</v>
       </c>
       <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920346</v>
+      </c>
+      <c r="B8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" t="s">
+        <v>105</v>
+      </c>
+      <c r="E8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920347</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9" t="s">
+        <v>108</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3APM - Estadisticos 20211.xlsx
+++ b/grupos/3APM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="117">
   <si>
     <t>Materia</t>
   </si>
@@ -158,22 +158,22 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
     <t>Castro Vasquez Julieta</t>
   </si>
   <si>
+    <t>De Jesús Orduña Sofía del Pilar</t>
+  </si>
+  <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
-    <t>Avila Coronado Julieta</t>
+    <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
     <t>Camarillo Aburto Raymundo</t>
-  </si>
-  <si>
-    <t>De Jesús Orduña Sofía del Pilar</t>
-  </si>
-  <si>
-    <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
     <t>NC</t>
@@ -890,40 +890,40 @@
         <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V4">
         <v>8</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -949,7 +949,7 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>8</v>
@@ -967,25 +967,25 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U5">
         <v>7</v>
@@ -994,13 +994,13 @@
         <v>6</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1044,22 +1044,22 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>8</v>
@@ -1103,10 +1103,10 @@
         <v>5</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>5</v>
@@ -1121,34 +1121,34 @@
         <v>5</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T7">
         <v>5</v>
       </c>
       <c r="U7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V7">
         <v>5</v>
       </c>
       <c r="W7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>5</v>
@@ -1180,10 +1180,10 @@
         <v>5</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J8">
         <v>5</v>
@@ -1198,25 +1198,25 @@
         <v>5</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U8">
         <v>5</v>
@@ -1257,7 +1257,7 @@
         <v>5</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I9">
         <v>6</v>
@@ -1275,28 +1275,28 @@
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T9">
         <v>5</v>
       </c>
       <c r="U9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -1305,7 +1305,7 @@
         <v>5</v>
       </c>
       <c r="X9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y9">
         <v>5</v>
@@ -1352,22 +1352,22 @@
         <v>5</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T10">
         <v>6</v>
@@ -1379,7 +1379,7 @@
         <v>8</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>5</v>
@@ -1411,10 +1411,10 @@
         <v>5</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J11">
         <v>5</v>
@@ -1429,22 +1429,22 @@
         <v>5</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T11">
         <v>5</v>
@@ -1506,22 +1506,22 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>9</v>
@@ -1530,7 +1530,7 @@
         <v>10</v>
       </c>
       <c r="V12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>10</v>
@@ -1583,40 +1583,40 @@
         <v>6</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U13">
         <v>6</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>9</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1660,28 +1660,28 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>8</v>
@@ -1690,7 +1690,7 @@
         <v>8</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>9</v>
@@ -1719,7 +1719,7 @@
         <v>7</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I15">
         <v>6</v>
@@ -1737,25 +1737,25 @@
         <v>6</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U15">
         <v>6</v>
@@ -1764,10 +1764,10 @@
         <v>6</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y15">
         <v>7</v>
@@ -1793,10 +1793,10 @@
         <v>7</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
         <v>5</v>
@@ -1808,34 +1808,34 @@
         <v>7</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>5</v>
       </c>
       <c r="U16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W16">
         <v>5</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1879,40 +1879,40 @@
         <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
         <v>8</v>
       </c>
       <c r="U17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y17">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1956,22 +1956,22 @@
         <v>8</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>10</v>
@@ -1980,7 +1980,7 @@
         <v>9</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>10</v>
@@ -2018,7 +2018,7 @@
         <v>7</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
         <v>5</v>
@@ -2033,28 +2033,28 @@
         <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T19">
         <v>8</v>
       </c>
       <c r="U19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>5</v>
@@ -2063,7 +2063,7 @@
         <v>5</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y19">
         <v>5</v>
@@ -2110,28 +2110,28 @@
         <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>9</v>
       </c>
       <c r="U20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>8</v>
@@ -2143,7 +2143,7 @@
         <v>9</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2187,22 +2187,22 @@
         <v>6</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T21">
         <v>9</v>
@@ -2211,7 +2211,7 @@
         <v>8</v>
       </c>
       <c r="V21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -2220,7 +2220,7 @@
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2264,22 +2264,22 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T22">
         <v>9</v>
@@ -2288,7 +2288,7 @@
         <v>9</v>
       </c>
       <c r="V22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W22">
         <v>9</v>
@@ -2341,22 +2341,22 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
         <v>7</v>
@@ -2365,10 +2365,10 @@
         <v>6</v>
       </c>
       <c r="V23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X23">
         <v>5</v>
@@ -2418,22 +2418,22 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>10</v>
@@ -2442,7 +2442,7 @@
         <v>9</v>
       </c>
       <c r="V24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W24">
         <v>10</v>
@@ -2495,31 +2495,31 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>10</v>
       </c>
       <c r="U25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W25">
         <v>10</v>
@@ -2572,40 +2572,40 @@
         <v>5</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U26">
         <v>6</v>
       </c>
       <c r="V26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>5</v>
       </c>
       <c r="Y26">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2649,22 +2649,22 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>10</v>
@@ -2673,7 +2673,7 @@
         <v>8</v>
       </c>
       <c r="V27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W27">
         <v>8</v>
@@ -2708,7 +2708,7 @@
         <v>6</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I28">
         <v>6</v>
@@ -2726,28 +2726,28 @@
         <v>5</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T28">
         <v>5</v>
       </c>
       <c r="U28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V28">
         <v>5</v>
@@ -2815,28 +2815,28 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>46</v>
       </c>
       <c r="C2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>45.83</v>
+        <v>60</v>
       </c>
       <c r="G2">
-        <v>54.17</v>
+        <v>40</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -2847,28 +2847,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>47</v>
       </c>
       <c r="C3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3">
         <v>16</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>64</v>
+        <v>66.67</v>
       </c>
       <c r="G3">
-        <v>36</v>
+        <v>33.33</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2879,7 +2879,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>48</v>
@@ -2900,7 +2900,7 @@
         <v>28</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2911,7 +2911,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>49</v>
@@ -2920,19 +2920,19 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G5">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2943,7 +2943,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>50</v>
@@ -2952,19 +2952,19 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G6">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2975,7 +2975,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>51</v>
@@ -2984,19 +2984,19 @@
         <v>25</v>
       </c>
       <c r="D7">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G7">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3502,7 +3502,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3534,22 +3534,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920337</v>
+        <v>20330051920340</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -3557,22 +3557,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920337</v>
+        <v>20330051920340</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -3580,22 +3580,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920340</v>
+        <v>20330051920354</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -3603,22 +3603,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920340</v>
+        <v>20330051920354</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -3638,10 +3638,10 @@
         <v>97</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -3649,19 +3649,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920345</v>
+        <v>20330051920337</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
         <v>46</v>
@@ -3672,47 +3672,24 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920346</v>
+        <v>20330051920356</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920347</v>
-      </c>
-      <c r="B9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" t="s">
-        <v>88</v>
-      </c>
-      <c r="D9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9">
         <v>5</v>
       </c>
     </row>
